--- a/ig/test-tabs-svs/ValueSet-jdv-j399-motivation-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j399-motivation-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="751">
   <si>
     <t>Property</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j399-motivation-ms|20260601120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -2586,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2619,14 +2616,6 @@
       </c>
       <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2641,40 +2630,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="F2" t="s" s="2">
         <v>15</v>
@@ -2685,17 +2674,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>15</v>
@@ -2706,17 +2695,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>15</v>
@@ -2727,17 +2716,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>15</v>
@@ -2748,17 +2737,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>15</v>
@@ -2769,17 +2758,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>15</v>
@@ -2790,17 +2779,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>15</v>
@@ -2811,17 +2800,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>15</v>
@@ -2832,17 +2821,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>15</v>
@@ -2853,17 +2842,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>15</v>
@@ -2874,17 +2863,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>15</v>
@@ -2895,17 +2884,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>71</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>15</v>
@@ -2916,17 +2905,17 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>15</v>
@@ -2937,17 +2926,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>15</v>
@@ -2958,17 +2947,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>15</v>
@@ -2979,17 +2968,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>15</v>
@@ -3000,17 +2989,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>15</v>
@@ -3021,17 +3010,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>15</v>
@@ -3042,17 +3031,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>15</v>
@@ -3063,17 +3052,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>15</v>
@@ -3084,17 +3073,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>15</v>
@@ -3105,17 +3094,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>15</v>
@@ -3126,17 +3115,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>15</v>
@@ -3147,17 +3136,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>15</v>
@@ -3168,17 +3157,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>15</v>
@@ -3189,17 +3178,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>15</v>
@@ -3210,17 +3199,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>15</v>
@@ -3231,17 +3220,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>15</v>
@@ -3252,17 +3241,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>15</v>
@@ -3273,17 +3262,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>15</v>
@@ -3294,17 +3283,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E32" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>15</v>
@@ -3315,17 +3304,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>15</v>
@@ -3336,17 +3325,17 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>15</v>
@@ -3357,17 +3346,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>15</v>
@@ -3378,17 +3367,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>15</v>
@@ -3399,17 +3388,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>15</v>
@@ -3420,17 +3409,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>15</v>
@@ -3441,17 +3430,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>15</v>
@@ -3462,17 +3451,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>15</v>
@@ -3483,17 +3472,17 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E41" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>15</v>
@@ -3504,17 +3493,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E42" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>15</v>
@@ -3525,17 +3514,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E43" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>15</v>
@@ -3546,17 +3535,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>15</v>
@@ -3567,17 +3556,17 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>15</v>
@@ -3588,17 +3577,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>15</v>
@@ -3609,17 +3598,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>15</v>
@@ -3630,17 +3619,17 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E48" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>15</v>
@@ -3651,17 +3640,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>15</v>
@@ -3672,17 +3661,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>15</v>
@@ -3693,17 +3682,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>15</v>
@@ -3714,17 +3703,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E52" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>15</v>
@@ -3735,17 +3724,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>15</v>
@@ -3756,17 +3745,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>15</v>
@@ -3777,17 +3766,17 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>15</v>
@@ -3798,17 +3787,17 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>15</v>
@@ -3819,17 +3808,17 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>15</v>
@@ -3840,17 +3829,17 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>15</v>
@@ -3861,17 +3850,17 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="E59" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="E59" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>15</v>
@@ -3882,17 +3871,17 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>15</v>
@@ -3903,17 +3892,17 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>15</v>
@@ -3924,17 +3913,17 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>15</v>
@@ -3945,17 +3934,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>15</v>
@@ -3966,17 +3955,17 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="E64" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="E64" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>15</v>
@@ -3987,17 +3976,17 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="E65" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>15</v>
@@ -4008,17 +3997,17 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>15</v>
@@ -4029,17 +4018,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E67" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>15</v>
@@ -4050,17 +4039,17 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E68" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>15</v>
@@ -4071,17 +4060,17 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>15</v>
@@ -4092,17 +4081,17 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>15</v>
@@ -4113,17 +4102,17 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>15</v>
@@ -4134,17 +4123,17 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="E72" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>15</v>
@@ -4155,17 +4144,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E73" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="E73" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>15</v>
@@ -4176,17 +4165,17 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="E74" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="E74" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>15</v>
@@ -4197,17 +4186,17 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="E75" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>15</v>
@@ -4218,17 +4207,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E76" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="E76" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>15</v>
@@ -4239,17 +4228,17 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="E77" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="E77" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>15</v>
@@ -4260,17 +4249,17 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="E78" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="E78" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>15</v>
@@ -4281,17 +4270,17 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="E79" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>15</v>
@@ -4302,17 +4291,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E80" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="E80" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>15</v>
@@ -4323,17 +4312,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>15</v>
@@ -4344,17 +4333,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="E82" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>15</v>
@@ -4365,17 +4354,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>15</v>
@@ -4386,17 +4375,17 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="E84" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="E84" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>15</v>
@@ -4407,17 +4396,17 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="E85" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>15</v>
@@ -4428,17 +4417,17 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="E86" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>15</v>
@@ -4449,17 +4438,17 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="E87" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="E87" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>15</v>
@@ -4470,17 +4459,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="E88" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="E88" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>15</v>
@@ -4491,17 +4480,17 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="E89" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>15</v>
@@ -4512,17 +4501,17 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="E90" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>15</v>
@@ -4533,17 +4522,17 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="E91" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>15</v>
@@ -4554,17 +4543,17 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="E92" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>15</v>
@@ -4575,17 +4564,17 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="E93" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>15</v>
@@ -4596,17 +4585,17 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E94" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>15</v>
@@ -4617,17 +4606,17 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="E95" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="E95" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>15</v>
@@ -4638,17 +4627,17 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="E96" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>15</v>
@@ -4659,17 +4648,17 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>15</v>
@@ -4680,17 +4669,17 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="E98" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>15</v>
@@ -4701,17 +4690,17 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="E99" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="E99" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>15</v>
@@ -4722,17 +4711,17 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="E100" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>15</v>
@@ -4743,17 +4732,17 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E101" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>15</v>
@@ -4764,17 +4753,17 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="E102" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>15</v>
@@ -4785,17 +4774,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="E103" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>15</v>
@@ -4806,17 +4795,17 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="E104" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>15</v>
@@ -4827,17 +4816,17 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="E105" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="E105" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>15</v>
@@ -4848,17 +4837,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="E106" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>15</v>
@@ -4869,17 +4858,17 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>15</v>
@@ -4890,17 +4879,17 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E108" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>15</v>
@@ -4911,17 +4900,17 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="E109" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="F109" t="s" s="2">
         <v>15</v>
@@ -4932,17 +4921,17 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="E110" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="E110" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="F110" t="s" s="2">
         <v>15</v>
@@ -4953,17 +4942,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="F111" t="s" s="2">
         <v>15</v>
@@ -4974,17 +4963,17 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="E112" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>15</v>
@@ -4995,17 +4984,17 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="E113" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="E113" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>15</v>
@@ -5016,17 +5005,17 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="E114" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="E114" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="F114" t="s" s="2">
         <v>15</v>
@@ -5037,17 +5026,17 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="E115" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="E115" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>15</v>
@@ -5058,17 +5047,17 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="E116" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="E116" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>15</v>
@@ -5079,17 +5068,17 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="E117" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="E117" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="F117" t="s" s="2">
         <v>15</v>
@@ -5100,17 +5089,17 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="E118" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="F118" t="s" s="2">
         <v>15</v>
@@ -5121,17 +5110,17 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="E119" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="E119" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>15</v>
@@ -5142,17 +5131,17 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="E120" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="E120" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>15</v>
@@ -5163,17 +5152,17 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="E121" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="E121" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="F121" t="s" s="2">
         <v>15</v>
@@ -5184,17 +5173,17 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="E122" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="E122" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="F122" t="s" s="2">
         <v>15</v>
@@ -5205,17 +5194,17 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="E123" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>15</v>
@@ -5226,17 +5215,17 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="E124" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="F124" t="s" s="2">
         <v>15</v>
@@ -5247,17 +5236,17 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="E125" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="E125" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="F125" t="s" s="2">
         <v>15</v>
@@ -5268,17 +5257,17 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="E126" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="E126" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="F126" t="s" s="2">
         <v>15</v>
@@ -5289,17 +5278,17 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="E127" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="E127" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="F127" t="s" s="2">
         <v>15</v>
@@ -5310,17 +5299,17 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="E128" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="E128" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>15</v>
@@ -5331,17 +5320,17 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="E129" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="E129" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="F129" t="s" s="2">
         <v>15</v>
@@ -5352,17 +5341,17 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="E130" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="E130" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="F130" t="s" s="2">
         <v>15</v>
@@ -5373,17 +5362,17 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="E131" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="E131" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>15</v>
@@ -5394,17 +5383,17 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="E132" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="E132" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="F132" t="s" s="2">
         <v>15</v>
@@ -5415,17 +5404,17 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="E133" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="E133" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="F133" t="s" s="2">
         <v>15</v>
@@ -5436,17 +5425,17 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E134" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="F134" t="s" s="2">
         <v>15</v>
@@ -5457,17 +5446,17 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="E135" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="E135" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="F135" t="s" s="2">
         <v>15</v>
@@ -5478,17 +5467,17 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="E136" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="E136" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="F136" t="s" s="2">
         <v>15</v>
@@ -5499,17 +5488,17 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="E137" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="E137" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>15</v>
@@ -5520,17 +5509,17 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="E138" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="E138" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="F138" t="s" s="2">
         <v>15</v>
@@ -5541,17 +5530,17 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="E139" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="E139" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="F139" t="s" s="2">
         <v>15</v>
@@ -5562,17 +5551,17 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="E140" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="E140" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="F140" t="s" s="2">
         <v>15</v>
@@ -5583,17 +5572,17 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="E141" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="E141" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="F141" t="s" s="2">
         <v>15</v>
@@ -5604,17 +5593,17 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="E142" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="E142" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="F142" t="s" s="2">
         <v>15</v>
@@ -5625,17 +5614,17 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="E143" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="E143" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="F143" t="s" s="2">
         <v>15</v>
@@ -5646,17 +5635,17 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="E144" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="E144" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="F144" t="s" s="2">
         <v>15</v>
@@ -5667,17 +5656,17 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E145" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="E145" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="F145" t="s" s="2">
         <v>15</v>
@@ -5688,17 +5677,17 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="E146" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="E146" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="F146" t="s" s="2">
         <v>15</v>
@@ -5709,17 +5698,17 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="E147" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="E147" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="F147" t="s" s="2">
         <v>15</v>
@@ -5730,17 +5719,17 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="E148" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="E148" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="F148" t="s" s="2">
         <v>15</v>
@@ -5751,17 +5740,17 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="E149" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="E149" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>15</v>
@@ -5772,17 +5761,17 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="E150" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="E150" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="F150" t="s" s="2">
         <v>15</v>
@@ -5793,17 +5782,17 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="E151" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="E151" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="F151" t="s" s="2">
         <v>15</v>
@@ -5814,17 +5803,17 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="E152" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="E152" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="F152" t="s" s="2">
         <v>15</v>
@@ -5835,17 +5824,17 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="E153" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="E153" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>15</v>
@@ -5856,17 +5845,17 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="E154" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="E154" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>15</v>
@@ -5877,17 +5866,17 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E155" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="E155" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>15</v>
@@ -5898,17 +5887,17 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="E156" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="E156" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>15</v>
@@ -5919,17 +5908,17 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="E157" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="E157" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="F157" t="s" s="2">
         <v>15</v>
@@ -5940,17 +5929,17 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E158" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="E158" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="F158" t="s" s="2">
         <v>15</v>
@@ -5961,17 +5950,17 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="E159" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="E159" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="F159" t="s" s="2">
         <v>15</v>
@@ -5982,17 +5971,17 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="E160" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="E160" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="F160" t="s" s="2">
         <v>15</v>
@@ -6003,17 +5992,17 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="E161" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="E161" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="F161" t="s" s="2">
         <v>15</v>
@@ -6024,17 +6013,17 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E162" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="E162" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="F162" t="s" s="2">
         <v>15</v>
@@ -6045,17 +6034,17 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="E163" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="E163" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>15</v>
@@ -6066,17 +6055,17 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="E164" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="E164" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="F164" t="s" s="2">
         <v>15</v>
@@ -6087,17 +6076,17 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="E165" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="E165" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>15</v>
@@ -6108,17 +6097,17 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E166" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="E166" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>15</v>
@@ -6129,17 +6118,17 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="E167" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="E167" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="F167" t="s" s="2">
         <v>15</v>
@@ -6150,17 +6139,17 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="E168" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="E168" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="F168" t="s" s="2">
         <v>15</v>
@@ -6171,17 +6160,17 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="E169" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="E169" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="F169" t="s" s="2">
         <v>15</v>
@@ -6192,17 +6181,17 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E170" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="E170" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="F170" t="s" s="2">
         <v>15</v>
@@ -6213,17 +6202,17 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="E171" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="E171" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>15</v>
@@ -6234,17 +6223,17 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="E172" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="E172" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="F172" t="s" s="2">
         <v>15</v>
@@ -6255,17 +6244,17 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="E173" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="E173" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="F173" t="s" s="2">
         <v>15</v>
@@ -6276,17 +6265,17 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="E174" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="E174" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="F174" t="s" s="2">
         <v>15</v>
@@ -6297,17 +6286,17 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="E175" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="E175" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="F175" t="s" s="2">
         <v>15</v>
@@ -6318,17 +6307,17 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="E176" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="E176" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="F176" t="s" s="2">
         <v>15</v>
@@ -6339,17 +6328,17 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="E177" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="E177" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="F177" t="s" s="2">
         <v>15</v>
@@ -6360,17 +6349,17 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="E178" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="E178" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="F178" t="s" s="2">
         <v>15</v>
@@ -6381,17 +6370,17 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="E179" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="E179" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="F179" t="s" s="2">
         <v>15</v>
@@ -6402,17 +6391,17 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="E180" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="E180" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="F180" t="s" s="2">
         <v>15</v>
@@ -6423,17 +6412,17 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="E181" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="E181" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="F181" t="s" s="2">
         <v>15</v>
@@ -6444,17 +6433,17 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="E182" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="E182" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="F182" t="s" s="2">
         <v>15</v>
@@ -6465,17 +6454,17 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="E183" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="E183" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="F183" t="s" s="2">
         <v>15</v>
@@ -6486,17 +6475,17 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="E184" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="E184" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="F184" t="s" s="2">
         <v>15</v>
@@ -6507,17 +6496,17 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="E185" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="E185" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="F185" t="s" s="2">
         <v>15</v>
@@ -6528,17 +6517,17 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="E186" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="E186" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="F186" t="s" s="2">
         <v>15</v>
@@ -6549,17 +6538,17 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E187" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="E187" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>15</v>
@@ -6570,17 +6559,17 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="E188" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="E188" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="F188" t="s" s="2">
         <v>15</v>
@@ -6591,17 +6580,17 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="E189" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="E189" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="F189" t="s" s="2">
         <v>15</v>
@@ -6612,17 +6601,17 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="E190" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="E190" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="F190" t="s" s="2">
         <v>15</v>
@@ -6633,17 +6622,17 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="E191" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="E191" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="F191" t="s" s="2">
         <v>15</v>
@@ -6654,17 +6643,17 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="E192" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="E192" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="F192" t="s" s="2">
         <v>15</v>
@@ -6675,17 +6664,17 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="E193" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="E193" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="F193" t="s" s="2">
         <v>15</v>
@@ -6696,17 +6685,17 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E194" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="E194" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="F194" t="s" s="2">
         <v>15</v>
@@ -6717,17 +6706,17 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="E195" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="E195" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="F195" t="s" s="2">
         <v>15</v>
@@ -6738,17 +6727,17 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="E196" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="E196" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="F196" t="s" s="2">
         <v>15</v>
@@ -6759,17 +6748,17 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="E197" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="E197" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="F197" t="s" s="2">
         <v>15</v>
@@ -6780,17 +6769,17 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="E198" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="E198" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="F198" t="s" s="2">
         <v>15</v>
@@ -6801,17 +6790,17 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="E199" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="E199" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="F199" t="s" s="2">
         <v>15</v>
@@ -6822,17 +6811,17 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="E200" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="E200" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="F200" t="s" s="2">
         <v>15</v>
@@ -6843,17 +6832,17 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E201" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="E201" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="F201" t="s" s="2">
         <v>15</v>
@@ -6864,17 +6853,17 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E202" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="E202" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="F202" t="s" s="2">
         <v>15</v>
@@ -6885,17 +6874,17 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="E203" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="E203" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="F203" t="s" s="2">
         <v>15</v>
@@ -6906,17 +6895,17 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="E204" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="E204" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="F204" t="s" s="2">
         <v>15</v>
@@ -6927,17 +6916,17 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E205" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="E205" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="F205" t="s" s="2">
         <v>15</v>
@@ -6948,17 +6937,17 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="E206" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="E206" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="F206" t="s" s="2">
         <v>15</v>
@@ -6969,17 +6958,17 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="E207" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="E207" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="F207" t="s" s="2">
         <v>15</v>
@@ -6990,17 +6979,17 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="E208" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="E208" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="F208" t="s" s="2">
         <v>15</v>
@@ -7011,17 +7000,17 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="E209" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="E209" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="F209" t="s" s="2">
         <v>15</v>
@@ -7032,17 +7021,17 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="E210" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="E210" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="F210" t="s" s="2">
         <v>15</v>
@@ -7053,17 +7042,17 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="E211" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="E211" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="F211" t="s" s="2">
         <v>15</v>
@@ -7074,17 +7063,17 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E212" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="E212" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="F212" t="s" s="2">
         <v>15</v>
@@ -7095,17 +7084,17 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="E213" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="E213" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="F213" t="s" s="2">
         <v>15</v>
@@ -7116,17 +7105,17 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E214" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="E214" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="F214" t="s" s="2">
         <v>15</v>
@@ -7137,17 +7126,17 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="E215" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="E215" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="F215" t="s" s="2">
         <v>15</v>
@@ -7158,17 +7147,17 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="E216" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="E216" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="F216" t="s" s="2">
         <v>15</v>
@@ -7179,17 +7168,17 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E217" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="E217" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="F217" t="s" s="2">
         <v>15</v>
@@ -7200,17 +7189,17 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="E218" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="E218" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="F218" t="s" s="2">
         <v>15</v>
@@ -7221,17 +7210,17 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="E219" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="E219" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="F219" t="s" s="2">
         <v>15</v>
@@ -7242,17 +7231,17 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="E220" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="E220" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="F220" t="s" s="2">
         <v>15</v>
@@ -7263,17 +7252,17 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E221" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="E221" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="F221" t="s" s="2">
         <v>15</v>
@@ -7284,17 +7273,17 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="E222" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="E222" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="F222" t="s" s="2">
         <v>15</v>
@@ -7305,17 +7294,17 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="E223" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="E223" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="F223" t="s" s="2">
         <v>15</v>
@@ -7326,17 +7315,17 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="E224" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="E224" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="F224" t="s" s="2">
         <v>15</v>
@@ -7347,17 +7336,17 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E225" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="E225" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="F225" t="s" s="2">
         <v>15</v>
@@ -7368,17 +7357,17 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="E226" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="E226" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="F226" t="s" s="2">
         <v>15</v>
@@ -7389,17 +7378,17 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="E227" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="E227" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="F227" t="s" s="2">
         <v>15</v>
@@ -7410,17 +7399,17 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="E228" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="E228" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="F228" t="s" s="2">
         <v>15</v>
@@ -7431,17 +7420,17 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="E229" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="E229" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="F229" t="s" s="2">
         <v>15</v>
@@ -7452,17 +7441,17 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E230" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="E230" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="F230" t="s" s="2">
         <v>15</v>
@@ -7473,17 +7462,17 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="E231" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="E231" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="F231" t="s" s="2">
         <v>15</v>
@@ -7494,17 +7483,17 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="E232" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="E232" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="F232" t="s" s="2">
         <v>15</v>
@@ -7515,17 +7504,17 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="E233" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="E233" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="F233" t="s" s="2">
         <v>15</v>
@@ -7536,17 +7525,17 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="E234" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="E234" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="F234" t="s" s="2">
         <v>15</v>
@@ -7557,17 +7546,17 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="E235" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="E235" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="F235" t="s" s="2">
         <v>15</v>
@@ -7578,17 +7567,17 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="E236" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="E236" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="F236" t="s" s="2">
         <v>15</v>
@@ -7599,17 +7588,17 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="E237" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="E237" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="F237" t="s" s="2">
         <v>15</v>
@@ -7620,17 +7609,17 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="E238" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="E238" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="F238" t="s" s="2">
         <v>15</v>
@@ -7641,17 +7630,17 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="E239" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="E239" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="F239" t="s" s="2">
         <v>15</v>
@@ -7662,17 +7651,17 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="E240" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="E240" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="F240" t="s" s="2">
         <v>15</v>
@@ -7683,17 +7672,17 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="E241" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="E241" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="F241" t="s" s="2">
         <v>15</v>
@@ -7704,17 +7693,17 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="E242" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="E242" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="F242" t="s" s="2">
         <v>15</v>
@@ -7725,17 +7714,17 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="E243" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="E243" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="F243" t="s" s="2">
         <v>15</v>
@@ -7746,17 +7735,17 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="E244" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="E244" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="F244" t="s" s="2">
         <v>15</v>
@@ -7767,17 +7756,17 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="E245" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="E245" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="F245" t="s" s="2">
         <v>15</v>
@@ -7788,17 +7777,17 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="E246" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="E246" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="F246" t="s" s="2">
         <v>15</v>
@@ -7809,17 +7798,17 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="E247" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="E247" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="F247" t="s" s="2">
         <v>15</v>
@@ -7830,17 +7819,17 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="E248" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="E248" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="F248" t="s" s="2">
         <v>15</v>
@@ -7851,17 +7840,17 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="E249" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="E249" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="F249" t="s" s="2">
         <v>15</v>
@@ -7872,17 +7861,17 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="E250" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="E250" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="F250" t="s" s="2">
         <v>15</v>
@@ -7893,17 +7882,17 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="E251" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="E251" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="F251" t="s" s="2">
         <v>15</v>
@@ -7914,17 +7903,17 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="E252" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="E252" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="F252" t="s" s="2">
         <v>15</v>
@@ -7935,17 +7924,17 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E253" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="E253" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="F253" t="s" s="2">
         <v>15</v>
@@ -7956,17 +7945,17 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="E254" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="E254" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="F254" t="s" s="2">
         <v>15</v>
@@ -7977,17 +7966,17 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="E255" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="E255" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="F255" t="s" s="2">
         <v>15</v>
@@ -7998,17 +7987,17 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E256" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="E256" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="F256" t="s" s="2">
         <v>15</v>
@@ -8019,17 +8008,17 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="E257" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="E257" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="F257" t="s" s="2">
         <v>15</v>
@@ -8040,17 +8029,17 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="E258" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="E258" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="F258" t="s" s="2">
         <v>15</v>
@@ -8061,17 +8050,17 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="E259" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="E259" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="F259" t="s" s="2">
         <v>15</v>
@@ -8082,17 +8071,17 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="E260" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="E260" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="F260" t="s" s="2">
         <v>15</v>
@@ -8103,17 +8092,17 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="E261" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="E261" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="F261" t="s" s="2">
         <v>15</v>
@@ -8124,17 +8113,17 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="E262" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="E262" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="F262" t="s" s="2">
         <v>15</v>
@@ -8145,17 +8134,17 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E263" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="E263" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="F263" t="s" s="2">
         <v>15</v>
@@ -8166,17 +8155,17 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E264" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="E264" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="F264" t="s" s="2">
         <v>15</v>
@@ -8187,17 +8176,17 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="E265" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="E265" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="F265" t="s" s="2">
         <v>15</v>
@@ -8208,17 +8197,17 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="E266" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="E266" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="F266" t="s" s="2">
         <v>15</v>
@@ -8229,17 +8218,17 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="E267" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="E267" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="F267" t="s" s="2">
         <v>15</v>
@@ -8250,17 +8239,17 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="E268" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="E268" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="F268" t="s" s="2">
         <v>15</v>
@@ -8271,17 +8260,17 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E269" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="E269" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="F269" t="s" s="2">
         <v>15</v>
@@ -8292,17 +8281,17 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="E270" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="E270" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="F270" t="s" s="2">
         <v>15</v>
@@ -8313,17 +8302,17 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="E271" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="E271" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="F271" t="s" s="2">
         <v>15</v>
@@ -8334,17 +8323,17 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="E272" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="E272" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="F272" t="s" s="2">
         <v>15</v>
@@ -8355,17 +8344,17 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="E273" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="E273" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="F273" t="s" s="2">
         <v>15</v>
@@ -8376,17 +8365,17 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="E274" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="E274" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="F274" t="s" s="2">
         <v>15</v>
@@ -8397,17 +8386,17 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="E275" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="E275" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="F275" t="s" s="2">
         <v>15</v>
@@ -8418,17 +8407,17 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="E276" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="E276" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="F276" t="s" s="2">
         <v>15</v>
@@ -8439,17 +8428,17 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="E277" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="E277" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="F277" t="s" s="2">
         <v>15</v>
@@ -8460,17 +8449,17 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="E278" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="E278" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="F278" t="s" s="2">
         <v>15</v>
@@ -8481,17 +8470,17 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="E279" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="E279" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="F279" t="s" s="2">
         <v>15</v>
@@ -8502,17 +8491,17 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="E280" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="E280" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="F280" t="s" s="2">
         <v>15</v>
@@ -8523,17 +8512,17 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="E281" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="E281" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="F281" t="s" s="2">
         <v>15</v>
@@ -8544,17 +8533,17 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="E282" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="E282" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="F282" t="s" s="2">
         <v>15</v>
@@ -8565,17 +8554,17 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="E283" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="E283" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="F283" t="s" s="2">
         <v>15</v>
@@ -8586,17 +8575,17 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="E284" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="E284" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="F284" t="s" s="2">
         <v>15</v>
@@ -8607,17 +8596,17 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="E285" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="E285" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="F285" t="s" s="2">
         <v>15</v>
@@ -8628,17 +8617,17 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="E286" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="E286" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="F286" t="s" s="2">
         <v>15</v>
@@ -8649,17 +8638,17 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="E287" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="E287" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="F287" t="s" s="2">
         <v>15</v>
@@ -8670,17 +8659,17 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="E288" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="E288" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="F288" t="s" s="2">
         <v>15</v>
@@ -8691,17 +8680,17 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="E289" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="E289" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="F289" t="s" s="2">
         <v>15</v>
@@ -8712,17 +8701,17 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="E290" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="E290" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="F290" t="s" s="2">
         <v>15</v>
@@ -8733,17 +8722,17 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="E291" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="E291" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="F291" t="s" s="2">
         <v>15</v>
@@ -8754,17 +8743,17 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="E292" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="E292" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="F292" t="s" s="2">
         <v>15</v>
@@ -8775,17 +8764,17 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="E293" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="E293" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="F293" t="s" s="2">
         <v>15</v>
@@ -8796,17 +8785,17 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="E294" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="E294" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="F294" t="s" s="2">
         <v>15</v>
@@ -8817,17 +8806,17 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E295" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="E295" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="F295" t="s" s="2">
         <v>15</v>
@@ -8838,17 +8827,17 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="E296" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="E296" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="F296" t="s" s="2">
         <v>15</v>
@@ -8859,17 +8848,17 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="E297" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="E297" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="F297" t="s" s="2">
         <v>15</v>
@@ -8880,17 +8869,17 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="E298" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="E298" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="F298" t="s" s="2">
         <v>15</v>
@@ -8901,17 +8890,17 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="E299" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="E299" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="F299" t="s" s="2">
         <v>15</v>
@@ -8922,17 +8911,17 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="E300" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="E300" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="F300" t="s" s="2">
         <v>15</v>
@@ -8943,17 +8932,17 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="E301" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="E301" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="F301" t="s" s="2">
         <v>15</v>
@@ -8964,17 +8953,17 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="E302" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="E302" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="F302" t="s" s="2">
         <v>15</v>
@@ -8985,17 +8974,17 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="E303" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="E303" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="F303" t="s" s="2">
         <v>15</v>
@@ -9006,17 +8995,17 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="E304" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="E304" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="F304" t="s" s="2">
         <v>15</v>
@@ -9027,17 +9016,17 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="E305" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="E305" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="F305" t="s" s="2">
         <v>15</v>
@@ -9048,17 +9037,17 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="E306" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="E306" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="F306" t="s" s="2">
         <v>15</v>
@@ -9069,17 +9058,17 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="E307" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="E307" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="F307" t="s" s="2">
         <v>15</v>
@@ -9090,17 +9079,17 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="E308" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="E308" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="F308" t="s" s="2">
         <v>15</v>
@@ -9111,17 +9100,17 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="E309" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="E309" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="F309" t="s" s="2">
         <v>15</v>
@@ -9132,17 +9121,17 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="E310" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="E310" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="F310" t="s" s="2">
         <v>15</v>
@@ -9153,17 +9142,17 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="E311" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="E311" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="F311" t="s" s="2">
         <v>15</v>
@@ -9174,17 +9163,17 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="E312" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="E312" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="F312" t="s" s="2">
         <v>15</v>
@@ -9195,17 +9184,17 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="E313" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="E313" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="F313" t="s" s="2">
         <v>15</v>
@@ -9216,17 +9205,17 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="E314" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="E314" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="F314" t="s" s="2">
         <v>15</v>
@@ -9237,17 +9226,17 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="E315" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="E315" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="F315" t="s" s="2">
         <v>15</v>
@@ -9258,17 +9247,17 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="E316" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="E316" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="F316" t="s" s="2">
         <v>15</v>
@@ -9279,17 +9268,17 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="E317" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="E317" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="F317" t="s" s="2">
         <v>15</v>
@@ -9300,17 +9289,17 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="E318" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="E318" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="F318" t="s" s="2">
         <v>15</v>
@@ -9321,17 +9310,17 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="E319" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="E319" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="F319" t="s" s="2">
         <v>15</v>
@@ -9342,17 +9331,17 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="E320" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="E320" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="F320" t="s" s="2">
         <v>15</v>
@@ -9363,17 +9352,17 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="E321" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="E321" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="F321" t="s" s="2">
         <v>15</v>
@@ -9384,17 +9373,17 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="E322" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="E322" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="F322" t="s" s="2">
         <v>15</v>
@@ -9405,17 +9394,17 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="E323" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="E323" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="F323" t="s" s="2">
         <v>15</v>
@@ -9426,17 +9415,17 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="E324" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="E324" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="F324" t="s" s="2">
         <v>15</v>
@@ -9447,17 +9436,17 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="E325" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="E325" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="F325" t="s" s="2">
         <v>15</v>
@@ -9468,17 +9457,17 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="E326" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="E326" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="F326" t="s" s="2">
         <v>15</v>
@@ -9489,17 +9478,17 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="E327" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="E327" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="F327" t="s" s="2">
         <v>15</v>
@@ -9510,17 +9499,17 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="E328" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="E328" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="F328" t="s" s="2">
         <v>15</v>
@@ -9531,17 +9520,17 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="E329" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="E329" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="F329" t="s" s="2">
         <v>15</v>
@@ -9552,17 +9541,17 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="E330" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="E330" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="F330" t="s" s="2">
         <v>15</v>
@@ -9573,17 +9562,17 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="E331" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="E331" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="F331" t="s" s="2">
         <v>15</v>
@@ -9594,17 +9583,17 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="E332" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="E332" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="F332" t="s" s="2">
         <v>15</v>
@@ -9615,17 +9604,17 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="E333" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="E333" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="F333" t="s" s="2">
         <v>15</v>
@@ -9636,17 +9625,17 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="E334" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="E334" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="F334" t="s" s="2">
         <v>15</v>
@@ -9657,17 +9646,17 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="E335" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="E335" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="F335" t="s" s="2">
         <v>15</v>
@@ -9678,17 +9667,17 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="E336" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="E336" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="F336" t="s" s="2">
         <v>15</v>
@@ -9699,17 +9688,17 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="E337" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="E337" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="F337" t="s" s="2">
         <v>15</v>
@@ -9720,17 +9709,17 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="E338" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="E338" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="F338" t="s" s="2">
         <v>15</v>
@@ -9741,17 +9730,17 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="E339" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="E339" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="F339" t="s" s="2">
         <v>15</v>
@@ -9762,17 +9751,17 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="E340" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="E340" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="F340" t="s" s="2">
         <v>15</v>
@@ -9783,17 +9772,17 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="E341" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="E341" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="F341" t="s" s="2">
         <v>15</v>
@@ -9804,17 +9793,17 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="E342" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="E342" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="F342" t="s" s="2">
         <v>15</v>
@@ -9825,17 +9814,17 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="E343" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="E343" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="F343" t="s" s="2">
         <v>15</v>
@@ -9846,17 +9835,17 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="E344" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="E344" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="F344" t="s" s="2">
         <v>15</v>
@@ -9867,17 +9856,17 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="E345" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="E345" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="F345" t="s" s="2">
         <v>15</v>
@@ -9888,17 +9877,17 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="E346" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="E346" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="F346" t="s" s="2">
         <v>15</v>
@@ -9909,17 +9898,17 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="E347" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="E347" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="F347" t="s" s="2">
         <v>15</v>
@@ -9930,17 +9919,17 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="E348" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="E348" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="F348" t="s" s="2">
         <v>15</v>
@@ -9951,17 +9940,17 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="E349" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="E349" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="F349" t="s" s="2">
         <v>15</v>
@@ -9972,17 +9961,17 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="E350" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="E350" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="F350" t="s" s="2">
         <v>15</v>
@@ -9993,17 +9982,17 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="E351" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="E351" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="F351" t="s" s="2">
         <v>15</v>
@@ -10014,17 +10003,17 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="E352" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="E352" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="F352" t="s" s="2">
         <v>15</v>
@@ -10035,17 +10024,17 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="E353" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="E353" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="F353" t="s" s="2">
         <v>15</v>
